--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>28/09 10:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>225</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>28/09 16:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>200</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>30/09 17:45</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>175</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>28/09 16:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>200</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>28/09 14:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>175</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>28/09 12:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>175</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>30/09 15:30</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>175</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>28/09 14:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>175</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>28/09 14:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>175</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>28/09 14:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>175</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>28/09 17:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>175</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>28/09 14:30</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>175</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>30/09 17:45</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>140</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>30/09 17:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>150</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>28/09 13:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>150</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>28/09 13:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>150</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>28/09 14:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>150</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>28/09 14:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>140</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>28/09 12:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>140</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>28/09 14:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>140</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>30/09 15:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>140</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>28/09 16:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>140</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>30/09 17:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>125</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>28/09 15:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>125</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>28/09 14:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>125</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,142 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45928.0742485552</v>
+        <v>45928.07424855324</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kosice – Z</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Kosice – ZvolenSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>28/09 14:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+110%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45928.13183206271</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lugano – A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Lugano – Ambri PiottaSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>30/09 17:45</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+89,2%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45928.13183206271</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | EHC Biel-B</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EHC Biel-Bienne – ZugSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>30/09 17:45</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+88,7%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45928.13183206271</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -1580,10 +1580,8 @@
           <t>28/09 14:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>150</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45928.13183206271</v>
+        <v>45928.13183206019</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>30/09 17:45</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>110</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45928.13183206271</v>
+        <v>45928.13183206019</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>30/09 17:45</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>110</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45928.13183206271</v>
+        <v>45928.13183206019</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1683,6 +1683,51 @@
         <v>45928.13183206019</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Eisbären B</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Eisbären Berlin – Schwenninger Wild WingsAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>28/09 12:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+154%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45928.22178761371</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>28/09 12:00</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>200</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,52 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45928.22178761371</v>
+        <v>45928.22178761574</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Bolzano – </t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Bolzano – Black Wings LinzICE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>28/09 16:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+160%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45928.27045513237</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>28/09 16:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>175</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,52 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45928.27045513237</v>
+        <v>45928.27045512731</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Orebro HK </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Orebro HK – Djurgaardens IFSHL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>30/09 17:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+97,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45928.30422945691</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,23 +1795,246 @@
           <t>30/09 17:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="n">
+        <v>125</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+97,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45928.30422945602</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EHC Munich</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EHC Munich – IserlohnDEL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>28/09 14:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+148%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45928.35050876964</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Salzbourg </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Salzbourg – Pioneers Vorarlberg385076e7 Autriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>28/09 13:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+146%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45928.35050876964</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Adler Mann</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Adler Mannheim – Lowen FrankfurtDEL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>28/09 14:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+122%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45928.35050876964</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Örebro HK </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Örebro HK – Djurgårdens IFSuède - Suède SHL A9ZJ2X7R 385076e7</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>30/09 17:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+110%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45928.35050876964</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Linkopings</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Linkopings – Farjestads BKSHL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>30/09 17:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>+97,0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>45928.30422945691</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+93,2%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45928.35050876964</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>28/09 14:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>175</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45928.35050876964</v>
+        <v>45928.35050877315</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>28/09 13:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>175</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45928.35050876964</v>
+        <v>45928.35050877315</v>
       </c>
     </row>
     <row r="35">
@@ -1928,10 +1924,8 @@
           <t>28/09 14:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>150</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1944,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45928.35050876964</v>
+        <v>45928.35050877315</v>
       </c>
     </row>
     <row r="36">
@@ -1973,10 +1967,8 @@
           <t>30/09 17:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>140</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1989,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45928.35050876964</v>
+        <v>45928.35050877315</v>
       </c>
     </row>
     <row r="37">
@@ -2018,10 +2010,8 @@
           <t>30/09 17:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>125</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2034,7 +2024,52 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45928.35050876964</v>
+        <v>45928.35050877315</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | SC Rappers</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SC Rapperswil-Jona Lakers – HC DavosNational League A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>30/09 17:45</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+214%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45928.38846796784</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2053,23 +2053,156 @@
           <t>30/09 17:45</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="n">
+        <v>200</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+214%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45928.38846796296</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Olimpija L</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Olimpija Ljubljana – Fehervar AV19Autriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>28/09 16:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>200.00</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>+214%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>45928.38846796784</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+176%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45928.4305183705</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | SCL Tigers</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SCL Tigers – Genève-ServetteNational League A</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>30/09 17:45</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+166%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45928.4305183705</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Nurnberg I</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Nurnberg Ice Tigers – DresdnerAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>28/09 14:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+135%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45928.4305183705</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,10 +2096,8 @@
           <t>28/09 16:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>200</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45928.4305183705</v>
+        <v>45928.43051836806</v>
       </c>
     </row>
     <row r="40">
@@ -2141,10 +2139,8 @@
           <t>30/09 17:45</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>175</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2157,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45928.4305183705</v>
+        <v>45928.43051836806</v>
       </c>
     </row>
     <row r="41">
@@ -2186,10 +2182,8 @@
           <t>28/09 14:30</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>175</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2202,7 +2196,97 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45928.4305183705</v>
+        <v>45928.43051836806</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Spisska No</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Spisska Nova Ves – NitraExtraliga</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>28/09 14:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+119%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45928.46975920167</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Liptovsky </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Liptovsky Mikulas – Banska BystricaSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>28/09 16:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+105%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45928.46975920167</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,10 +2225,8 @@
           <t>28/09 14:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>150</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45928.46975920167</v>
+        <v>45928.46975920139</v>
       </c>
     </row>
     <row r="43">
@@ -2270,10 +2268,8 @@
           <t>28/09 16:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>150</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2286,7 +2282,97 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45928.46975920167</v>
+        <v>45928.46975920139</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Straubing </t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Straubing – AugsbourgDEL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>28/09 17:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+152%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45928.52706452202</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Skellefteå</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Skellefteå AIK – Luleå HFSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>30/09 17:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+77,6%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45928.52706452202</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2311,10 +2311,8 @@
           <t>28/09 17:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>175</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45928.52706452202</v>
+        <v>45928.52706452546</v>
       </c>
     </row>
     <row r="45">
@@ -2356,23 +2354,201 @@
           <t>30/09 17:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" t="n">
+        <v>125</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+77,6%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45928.52706452546</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | ZSC Lions </t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ZSC Lions – Kloten FlyersSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>30/09 17:45</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+164%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45928.55779312341</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Cologne Ha</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Cologne Haie – Grizzlys WolfsburgDEL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>28/09 14:30</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+155%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45928.55779312341</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Dukla Tren</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Dukla Trencin – HK PopradExtraliga</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>28/09 13:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+106%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45928.55779312341</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ajoie – La</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ajoie – LausanneSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>30/09 17:45</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>+77,6%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>45928.52706452202</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+90,6%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45928.55779312341</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,10 +2397,8 @@
           <t>30/09 17:45</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>175</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2413,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45928.55779312341</v>
+        <v>45928.557793125</v>
       </c>
     </row>
     <row r="47">
@@ -2442,10 +2440,8 @@
           <t>28/09 14:30</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>175</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2458,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45928.55779312341</v>
+        <v>45928.557793125</v>
       </c>
     </row>
     <row r="48">
@@ -2487,10 +2483,8 @@
           <t>28/09 13:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>140</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2503,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45928.55779312341</v>
+        <v>45928.557793125</v>
       </c>
     </row>
     <row r="49">
@@ -2532,10 +2526,8 @@
           <t>30/09 17:45</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>125</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2548,7 +2540,142 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45928.55779312341</v>
+        <v>45928.557793125</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Frölunda H</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Frölunda HC – Brynas IFSHL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>30/09 17:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+72,6%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45928.59493134062</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kometa Brn</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Kometa Brno – PardubiceRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>28/09 15:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+58,8%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45928.59493134062</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Bern – Fri</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Bern – Fribourg GotteronSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>30/09 17:45</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>89.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1,70%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+51,3%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45928.59493134062</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,10 +2569,8 @@
           <t>30/09 17:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>110</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2585,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45928.59493134062</v>
+        <v>45928.5949313426</v>
       </c>
     </row>
     <row r="51">
@@ -2614,10 +2612,8 @@
           <t>28/09 15:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>110</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2630,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45928.59493134062</v>
+        <v>45928.5949313426</v>
       </c>
     </row>
     <row r="52">
@@ -2659,10 +2655,8 @@
           <t>30/09 17:45</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>89.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>89</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2675,7 +2669,412 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45928.59493134062</v>
+        <v>45928.5949313426</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Ajoie P</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>HC Ajoie Porrentruy – LausanneNational League A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>30/09 17:45</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+98,9%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45928.63777216797</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HC Lugano </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HC Lugano – HC Ambri PiottaNational League A stq pr cu 385076e7</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>30/09 17:45</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+65,6%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45928.63777216797</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betsson(FR)Hockey | Pas de buts | HC Dynamo </t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HC Dynamo Moscou – Neftekhimik NijnekamskRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>29/09 16:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+51,5%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45928.63777216797</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betsson(FR)Hockey | Pas de buts | SKA Saint </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SKA Saint Pétersbourg – Torpedo Nijni NovgorodRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>29/09 16:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+47,2%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45928.63777216797</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Litvino</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HC Litvinov – Ceske BudejoviceExtraliga</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>28/09 15:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+41,2%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45928.63777216797</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betsson(FR)Hockey | Pas de buts | Metallurg </t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Metallurg Magnitogorsk – Sibir NovosibirskRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>29/09 14:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+37,1%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45928.63777216797</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 2.52e équipe | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Sparta Prague – Shamrock RoversEurope - Ligue Conférence</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>02/10 19:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+35,9%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45928.63777216797</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | Avtomobili</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Avtomobilist Ekaterinbourg – AK Bars KazanRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>29/09 14:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>90.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+35,4%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45928.63777216797</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 - tir cadré | Atlético M</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Atlético Madrid – Eintracht FrancfortEurope. Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>30/09 19:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>25,8%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+34,3%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45928.63777216797</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>30/09 17:45</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>125</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45928.63777216797</v>
+        <v>45928.63777216435</v>
       </c>
     </row>
     <row r="54">
@@ -2743,10 +2741,8 @@
           <t>30/09 17:45</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>100</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2759,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45928.63777216797</v>
+        <v>45928.63777216435</v>
       </c>
     </row>
     <row r="55">
@@ -2788,10 +2784,8 @@
           <t>29/09 16:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>101</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2804,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45928.63777216797</v>
+        <v>45928.63777216435</v>
       </c>
     </row>
     <row r="56">
@@ -2833,10 +2827,8 @@
           <t>29/09 16:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>101</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2849,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45928.63777216797</v>
+        <v>45928.63777216435</v>
       </c>
     </row>
     <row r="57">
@@ -2878,10 +2870,8 @@
           <t>28/09 15:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>90</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2894,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45928.63777216797</v>
+        <v>45928.63777216435</v>
       </c>
     </row>
     <row r="58">
@@ -2923,10 +2913,8 @@
           <t>29/09 14:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>90</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2939,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45928.63777216797</v>
+        <v>45928.63777216435</v>
       </c>
     </row>
     <row r="59">
@@ -2968,10 +2956,8 @@
           <t>02/10 19:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>60</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2984,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45928.63777216797</v>
+        <v>45928.63777216435</v>
       </c>
     </row>
     <row r="60">
@@ -3013,10 +2999,8 @@
           <t>29/09 14:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>90.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>90</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3029,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45928.63777216797</v>
+        <v>45928.63777216435</v>
       </c>
     </row>
     <row r="61">
@@ -3058,10 +3042,8 @@
           <t>30/09 19:00</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>5.20</t>
-        </is>
+      <c r="F61" t="n">
+        <v>5.2</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3074,7 +3056,187 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45928.63777216797</v>
+        <v>45928.63777216435</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – Radnicki KragujevacSuperLiga</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>28/09 17:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+29,3%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45928.68243293135</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Timra IK –</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Timra IK – Rogle BKSHL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>30/09 17:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>70.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+24,9%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45928.68243293135</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Atletico T</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Atletico Tucuman – CA PlatenseLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>04/10 22:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+24,2%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45928.68243293135</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Corinthian</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Corinthians – FlamengoSérie A</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>28/09 23:30</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+23,5%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45928.68243293135</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3085,10 +3085,8 @@
           <t>28/09 17:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F62" t="n">
+        <v>55</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3101,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45928.68243293135</v>
+        <v>45928.68243292824</v>
       </c>
     </row>
     <row r="63">
@@ -3130,10 +3128,8 @@
           <t>30/09 17:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>70</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3146,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45928.68243293135</v>
+        <v>45928.68243292824</v>
       </c>
     </row>
     <row r="64">
@@ -3175,10 +3171,8 @@
           <t>04/10 22:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>60</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3191,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45928.68243293135</v>
+        <v>45928.68243292824</v>
       </c>
     </row>
     <row r="65">
@@ -3220,10 +3214,8 @@
           <t>28/09 23:30</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>60</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3236,7 +3228,457 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45928.68243293135</v>
+        <v>45928.68243292824</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kärpät Oul</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Kärpät Oulu – Pelicans LahtiFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>01/10 15:30</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+154%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45928.71937356988</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | HIFK – Koo</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>HIFK – KooKooFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>01/10 15:30</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+115%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45928.71937356988</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Pardubice </t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Pardubice – LitvinovRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>30/09 16:00</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+94,0%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45928.71937356988</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Sparta Pra</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Sparta Prague – PlzenRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>30/09 16:30</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+70,3%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45928.71937356988</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Liberec – </t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Liberec – Mlada BoleslavRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>30/09 16:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+62,7%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45928.71937356988</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Trinec – K</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Trinec – Kometa BrnoRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>30/09 15:00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+60,3%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45928.71937356988</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Mountfield</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Mountfield HK – OlomoucRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>30/09 16:00</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+59,6%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45928.71937356988</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ceske Bude</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ceske Budejovice – VitkoviceRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>30/09 15:30</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+59,1%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45928.71937356988</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Sport Vaas</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Sport Vaasa – Ilves Tampere385076e7 Finlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>01/10 15:30</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>98.00</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+50,9%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45928.71937356988</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | HC Spartak</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>HC Spartak Moscou – Traktor TcheliabinskRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>30/09 16:30</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+44,2%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45928.71937356988</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3257,10 +3257,8 @@
           <t>01/10 15:30</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>175</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3273,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45928.71937356988</v>
+        <v>45928.71937356482</v>
       </c>
     </row>
     <row r="67">
@@ -3302,10 +3300,8 @@
           <t>01/10 15:30</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>150</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3318,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45928.71937356988</v>
+        <v>45928.71937356482</v>
       </c>
     </row>
     <row r="68">
@@ -3347,10 +3343,8 @@
           <t>30/09 16:00</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>140</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3363,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45928.71937356988</v>
+        <v>45928.71937356482</v>
       </c>
     </row>
     <row r="69">
@@ -3392,10 +3386,8 @@
           <t>30/09 16:30</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F69" t="n">
+        <v>125</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3408,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45928.71937356988</v>
+        <v>45928.71937356482</v>
       </c>
     </row>
     <row r="70">
@@ -3437,10 +3429,8 @@
           <t>30/09 16:00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F70" t="n">
+        <v>110</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3453,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45928.71937356988</v>
+        <v>45928.71937356482</v>
       </c>
     </row>
     <row r="71">
@@ -3482,10 +3472,8 @@
           <t>30/09 15:00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F71" t="n">
+        <v>110</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3498,7 +3486,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45928.71937356988</v>
+        <v>45928.71937356482</v>
       </c>
     </row>
     <row r="72">
@@ -3527,10 +3515,8 @@
           <t>30/09 16:00</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F72" t="n">
+        <v>110</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3543,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45928.71937356988</v>
+        <v>45928.71937356482</v>
       </c>
     </row>
     <row r="73">
@@ -3572,10 +3558,8 @@
           <t>30/09 15:30</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F73" t="n">
+        <v>110</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3588,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45928.71937356988</v>
+        <v>45928.71937356482</v>
       </c>
     </row>
     <row r="74">
@@ -3617,10 +3601,8 @@
           <t>01/10 15:30</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>98.00</t>
-        </is>
+      <c r="F74" t="n">
+        <v>98</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3633,7 +3615,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45928.71937356988</v>
+        <v>45928.71937356482</v>
       </c>
     </row>
     <row r="75">
@@ -3662,10 +3644,8 @@
           <t>30/09 16:30</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F75" t="n">
+        <v>101</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3678,7 +3658,187 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45928.71937356988</v>
+        <v>45928.71937356482</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | ZSC Lions </t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ZSC Lions – EHC KlotenNational League A</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>30/09 17:45</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+123%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45928.76868629207</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HIFK Helsi</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>HIFK Helsinki – KooKooLiiga</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>01/10 15:30</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+116%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45928.76868629207</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Ceske Bude</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ceske Budejovice – HC VitkoviceExtraliga</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>30/09 15:30</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+89,0%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45928.76868629207</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Bili Tygri</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Bili Tygri Liberec – BK Mlada BoleslavExtraliga</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>30/09 16:00</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+52,7%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45928.76868629207</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3687,10 +3687,8 @@
           <t>30/09 17:45</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F76" t="n">
+        <v>150</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3703,7 +3701,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45928.76868629207</v>
+        <v>45928.76868629629</v>
       </c>
     </row>
     <row r="77">
@@ -3732,10 +3730,8 @@
           <t>01/10 15:30</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F77" t="n">
+        <v>140</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3748,7 +3744,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45928.76868629207</v>
+        <v>45928.76868629629</v>
       </c>
     </row>
     <row r="78">
@@ -3777,10 +3773,8 @@
           <t>30/09 15:30</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F78" t="n">
+        <v>125</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3793,7 +3787,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45928.76868629207</v>
+        <v>45928.76868629629</v>
       </c>
     </row>
     <row r="79">
@@ -3822,23 +3816,156 @@
           <t>30/09 16:00</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" t="n">
+        <v>100</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+52,7%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45928.76868629629</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Kärpät Oul</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Kärpät Oulu – Pelicans LahtiLiiga stq pr cu 385076e7</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>01/10 15:30</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>+165%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45928.80201178828</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Vaasan Spo</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Vaasan Sport – Ilves TampereLiiga</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>01/10 15:30</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>+57,2%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>45928.80201178828</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kladno – K</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Kladno – Karlovy VaryRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>30/09 16:00</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>93.00</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>1,53%</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>+52,7%</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>45928.76868629207</v>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>+42,1%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>45928.80201178828</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3859,10 +3859,8 @@
           <t>01/10 15:30</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F80" t="n">
+        <v>175</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3875,7 +3873,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45928.80201178828</v>
+        <v>45928.80201179398</v>
       </c>
     </row>
     <row r="81">
@@ -3904,10 +3902,8 @@
           <t>01/10 15:30</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F81" t="n">
+        <v>100</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3920,7 +3916,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45928.80201178828</v>
+        <v>45928.80201179398</v>
       </c>
     </row>
     <row r="82">
@@ -3949,10 +3945,8 @@
           <t>30/09 16:00</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>93.00</t>
-        </is>
+      <c r="F82" t="n">
+        <v>93</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3965,7 +3959,97 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45928.80201178828</v>
+        <v>45928.80201179398</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EHC Biel –</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>EHC Biel – EV ZugNational League A</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>30/09 17:45</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>+75,6%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>45928.84800661552</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | SaiPa – HP</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SaiPa – HPKFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>01/10 15:30</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>+55,9%</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>45928.84800661552</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -3988,10 +3988,8 @@
           <t>30/09 17:45</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F83" t="n">
+        <v>110</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4004,7 +4002,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>45928.84800661552</v>
+        <v>45928.84800662037</v>
       </c>
     </row>
     <row r="84">
@@ -4033,10 +4031,8 @@
           <t>01/10 15:30</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F84" t="n">
+        <v>110</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4049,7 +4045,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>45928.84800661552</v>
+        <v>45928.84800662037</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4048,6 +4048,141 @@
         <v>45928.84800662037</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ingolstadt</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ingolstadt – Straubing TigersAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>03/10 14:30</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>+119%</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>45928.92950057826</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Augsbourg </t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Augsbourg – BerlinDEL</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>03/10 12:00</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>+113%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>45928.92950057826</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Wild Wings</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Wild Wings – Dresdner EislowenDEL</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>02/10 17:30</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1,20%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>+109%</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>45928.92950057826</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-09-28.xlsx
+++ b/data/valuebets_database_2025-09-28.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4074,10 +4074,8 @@
           <t>03/10 14:30</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F85" t="n">
+        <v>175</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4090,7 +4088,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>45928.92950057826</v>
+        <v>45928.92950057871</v>
       </c>
     </row>
     <row r="86">
@@ -4119,10 +4117,8 @@
           <t>03/10 12:00</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F86" t="n">
+        <v>175</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4135,7 +4131,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>45928.92950057826</v>
+        <v>45928.92950057871</v>
       </c>
     </row>
     <row r="87">
@@ -4164,23 +4160,246 @@
           <t>02/10 17:30</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" t="n">
+        <v>175</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1,20%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>+109%</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>45928.92950057871</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Iserlohn R</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Iserlohn Roosters – Löwen FrankfurtAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>02/10 17:30</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>1,20%</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>+109%</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>45928.92950057826</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>+158%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>45928.97108054293</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Schwenning</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Schwenninger Wild Wings – DresdnerAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>02/10 17:30</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>+157%</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>45928.97108054293</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Munich – W</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Munich – Wolfsburg GrizzlyAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>03/10 14:30</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>+130%</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>45928.97108054293</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Augsburger</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Augsburger Panther – Eisbären BerlinAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>03/10 12:00</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>+129%</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>45928.97108054293</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | SaiPa – Ha</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SaiPa – HameenlinnaLiiga</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>01/10 15:30</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>+71,4%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>45928.97108054293</v>
       </c>
     </row>
   </sheetData>
